--- a/data_files/Site glossary.xlsx
+++ b/data_files/Site glossary.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nih.sharepoint.com/sites/NCI-CBIIT-FNLCCDI/Shared Documents/CCDC (Data Catalog nee PODCat)/2-Executing/System Document/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="219" documentId="13_ncr:1_{CD305CA4-F6E6-494C-8D70-07316997D1EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D3B5150-772B-4719-8F1B-4F0757B1406E}"/>
+  <xr:revisionPtr revIDLastSave="309" documentId="13_ncr:1_{CD305CA4-F6E6-494C-8D70-07316997D1EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{98713CE7-89A7-4D47-99CF-C23702FE8572}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{4110CF64-F05A-4DD9-960E-BC3FCD1C46EE}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="456">
   <si>
     <t>Term Category</t>
   </si>
@@ -969,6 +969,444 @@
   </si>
   <si>
     <t>Cancer Complexity Knowledge Portal</t>
+  </si>
+  <si>
+    <t>AFCRN</t>
+  </si>
+  <si>
+    <t>PMGH</t>
+  </si>
+  <si>
+    <t>PPB</t>
+  </si>
+  <si>
+    <t>RNCE</t>
+  </si>
+  <si>
+    <t>SACHA</t>
+  </si>
+  <si>
+    <t>ASPIRE</t>
+  </si>
+  <si>
+    <t>CCR</t>
+  </si>
+  <si>
+    <t>ChCR</t>
+  </si>
+  <si>
+    <t>HoLISTIC</t>
+  </si>
+  <si>
+    <t>GLOW</t>
+  </si>
+  <si>
+    <t>NCR</t>
+  </si>
+  <si>
+    <t>DCR</t>
+  </si>
+  <si>
+    <t>DCCSS-LATER</t>
+  </si>
+  <si>
+    <t>FCR</t>
+  </si>
+  <si>
+    <t>MET</t>
+  </si>
+  <si>
+    <t>NCRJ</t>
+  </si>
+  <si>
+    <t>OCR</t>
+  </si>
+  <si>
+    <t>Australian Childhood Cancer Registry </t>
+  </si>
+  <si>
+    <t>African Cancer Registry Network</t>
+  </si>
+  <si>
+    <t>Australian Particle Therapy Clinical Quality Registry</t>
+  </si>
+  <si>
+    <t>California Cancer Registry</t>
+  </si>
+  <si>
+    <t>Swiss Childhood Cancer Registry</t>
+  </si>
+  <si>
+    <t>Dutch Childhood Cancer Survivor Study</t>
+  </si>
+  <si>
+    <t>Delhi Cancer Registry</t>
+  </si>
+  <si>
+    <t>Finnish Cancer Registry</t>
+  </si>
+  <si>
+    <t>Global nLPHL One Working Group</t>
+  </si>
+  <si>
+    <t>Hodgkin Lymphoma International Study for Individual Care</t>
+  </si>
+  <si>
+    <t>Malignant Endocrine Tumors Registry</t>
+  </si>
+  <si>
+    <t>Netherlands Cancer Registry</t>
+  </si>
+  <si>
+    <t>National Cancer Registry of Japan</t>
+  </si>
+  <si>
+    <t>Osaka Cancer Registry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Port Moresby General Hospital </t>
+  </si>
+  <si>
+    <t>The International Pleuropulmonary Blastoma/DICER1 Registry</t>
+  </si>
+  <si>
+    <t>French National Registry of Childhood Cancers</t>
+  </si>
+  <si>
+    <t>Secured Access to Innovative Medicines for Children with Cancer</t>
+  </si>
+  <si>
+    <t>GCCR</t>
+  </si>
+  <si>
+    <t>German Childhood Cancer Registry</t>
+  </si>
+  <si>
+    <t>REDECAN</t>
+  </si>
+  <si>
+    <t>Spanish Network of Cancer Registries</t>
+  </si>
+  <si>
+    <t>AIEOP</t>
+  </si>
+  <si>
+    <t>Italian Association of Pediatric Hematology, Oncology, and Science</t>
+  </si>
+  <si>
+    <t>NCC</t>
+  </si>
+  <si>
+    <t>Korea National Cancer Center</t>
+  </si>
+  <si>
+    <t>AEDV</t>
+  </si>
+  <si>
+    <t>Spanish Academy of Dermatology and Venereology</t>
+  </si>
+  <si>
+    <t>JNS</t>
+  </si>
+  <si>
+    <t>Japan Neurosurgical Society</t>
+  </si>
+  <si>
+    <t>KSA</t>
+  </si>
+  <si>
+    <t>Cantonal Hospital Aarau</t>
+  </si>
+  <si>
+    <t>NCCCR</t>
+  </si>
+  <si>
+    <t>North Carolina Central Cancer Registry</t>
+  </si>
+  <si>
+    <t>NCDB</t>
+  </si>
+  <si>
+    <t>National Cancer Database</t>
+  </si>
+  <si>
+    <t>NIPH</t>
+  </si>
+  <si>
+    <t>Norwegian Institute of Public Health</t>
+  </si>
+  <si>
+    <t>NOPHO</t>
+  </si>
+  <si>
+    <t>The Nordic Society of Paediatric Haematology and Oncology Biobank</t>
+  </si>
+  <si>
+    <t>HCC</t>
+  </si>
+  <si>
+    <t>Hematology Cancer Consortium</t>
+  </si>
+  <si>
+    <t>INFORM</t>
+  </si>
+  <si>
+    <t>INdividualized therapy FOr high-Risk childhood Malignancies</t>
+  </si>
+  <si>
+    <t>KHCC</t>
+  </si>
+  <si>
+    <t>King Hussein Cancer Center</t>
+  </si>
+  <si>
+    <t>MCTR</t>
+  </si>
+  <si>
+    <t>Montana Central Tumor Registry</t>
+  </si>
+  <si>
+    <t>TCR</t>
+  </si>
+  <si>
+    <t>Tasmanian Cancer Registry</t>
+  </si>
+  <si>
+    <t>ECR</t>
+  </si>
+  <si>
+    <t>Estonian Cancer Registry</t>
+  </si>
+  <si>
+    <t>TMCR</t>
+  </si>
+  <si>
+    <t>Tanzania - Mwanza Cancer Registry</t>
+  </si>
+  <si>
+    <t>ANTR</t>
+  </si>
+  <si>
+    <t>Alaska Native Tumor Registry</t>
+  </si>
+  <si>
+    <t>IAFN</t>
+  </si>
+  <si>
+    <t>Italian Association for the fight against Neuroblastoma ETS</t>
+  </si>
+  <si>
+    <t>HuPON</t>
+  </si>
+  <si>
+    <t>Hungarian Pediatric Oncology Network</t>
+  </si>
+  <si>
+    <t>CrCR</t>
+  </si>
+  <si>
+    <t>Croatian Cancer Registry</t>
+  </si>
+  <si>
+    <t>CyCR</t>
+  </si>
+  <si>
+    <t>Cyprus Cancer Registry</t>
+  </si>
+  <si>
+    <t>MNCR</t>
+  </si>
+  <si>
+    <t>Malta National Cancer Registry</t>
+  </si>
+  <si>
+    <t>PNCR</t>
+  </si>
+  <si>
+    <t>Portugal National Cancer Registry</t>
+  </si>
+  <si>
+    <t>SCR</t>
+  </si>
+  <si>
+    <t>Slovenian Cancer Registry</t>
+  </si>
+  <si>
+    <t>NCRU</t>
+  </si>
+  <si>
+    <t>National Cancer Registry of Ukraine</t>
+  </si>
+  <si>
+    <t>POGONIS</t>
+  </si>
+  <si>
+    <t>Pediatric Oncology Group of Ontario Networked Information System</t>
+  </si>
+  <si>
+    <t>UCR</t>
+  </si>
+  <si>
+    <t>Utah Cancer Registry</t>
+  </si>
+  <si>
+    <t>NCRI</t>
+  </si>
+  <si>
+    <t>National Cancer Registry Ireland</t>
+  </si>
+  <si>
+    <t>ICR</t>
+  </si>
+  <si>
+    <t>Iraqi Ministry of Health Cancer Registry</t>
+  </si>
+  <si>
+    <t>GPCR</t>
+  </si>
+  <si>
+    <t>Girona Population Cancer Registry</t>
+  </si>
+  <si>
+    <t>SHCNCC</t>
+  </si>
+  <si>
+    <t>Saudi Health Council National Cancer Center</t>
+  </si>
+  <si>
+    <t>IsraelCR</t>
+  </si>
+  <si>
+    <t>Israel Cancer Registry</t>
+  </si>
+  <si>
+    <t>GBACR</t>
+  </si>
+  <si>
+    <t>Greater Bay Area Cancer Registry</t>
+  </si>
+  <si>
+    <t>ZCR</t>
+  </si>
+  <si>
+    <t>Zurich Cancer Registry</t>
+  </si>
+  <si>
+    <t>RENAPE</t>
+  </si>
+  <si>
+    <t>National Network for the Management of Rare Peritoneal Tumors</t>
+  </si>
+  <si>
+    <t>INPCR</t>
+  </si>
+  <si>
+    <t>Iranian National Population-based Cancer Registry</t>
+  </si>
+  <si>
+    <t>NFR</t>
+  </si>
+  <si>
+    <t>Neurofibromatosis Registry</t>
+  </si>
+  <si>
+    <t>AIRTUM</t>
+  </si>
+  <si>
+    <t>Italian Association of Cancer Registries</t>
+  </si>
+  <si>
+    <t>MACR</t>
+  </si>
+  <si>
+    <t>Massachusetts Cancer Registry</t>
+  </si>
+  <si>
+    <t>Yorkshire </t>
+  </si>
+  <si>
+    <t>Yorkshire Specialist Register of Cancer in Children and Young People</t>
+  </si>
+  <si>
+    <t>TXCR</t>
+  </si>
+  <si>
+    <t>Texas Cancer Registry</t>
+  </si>
+  <si>
+    <t>ACD</t>
+  </si>
+  <si>
+    <t>Australian Cancer Database</t>
+  </si>
+  <si>
+    <t>EUROCARE</t>
+  </si>
+  <si>
+    <t>EUROpean CAncer REgistry</t>
+  </si>
+  <si>
+    <t>CSP</t>
+  </si>
+  <si>
+    <t>Cancer Survivor Program</t>
+  </si>
+  <si>
+    <t>NZCCR</t>
+  </si>
+  <si>
+    <t>New Zealand Children's Cancer Registry</t>
+  </si>
+  <si>
+    <t>ANCR</t>
+  </si>
+  <si>
+    <t>Austrian National Cancer Registry</t>
+  </si>
+  <si>
+    <t>GCR</t>
+  </si>
+  <si>
+    <t>Gliomatosis Cerebri Registry</t>
+  </si>
+  <si>
+    <t>NICR</t>
+  </si>
+  <si>
+    <t>Northern Ireland Cancer Registry</t>
+  </si>
+  <si>
+    <t>SNCR</t>
+  </si>
+  <si>
+    <t>Sweden National Cancer Registry</t>
+  </si>
+  <si>
+    <t>TWCR</t>
+  </si>
+  <si>
+    <t>Taiwan Cancer Registry</t>
+  </si>
+  <si>
+    <t>ENCR</t>
+  </si>
+  <si>
+    <t>European Network of Cancer Registries</t>
+  </si>
+  <si>
+    <t>SANCR</t>
+  </si>
+  <si>
+    <t>South African National Cancer Registry</t>
+  </si>
+  <si>
+    <t>GACCR</t>
+  </si>
+  <si>
+    <t>Georgia Comprehensive Cancer Registry</t>
+  </si>
+  <si>
+    <t>ACCR</t>
   </si>
 </sst>
 </file>
@@ -1446,12 +1884,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69208F35-5666-473F-97EF-CB7A96B85984}">
-  <dimension ref="A1:E141"/>
+  <dimension ref="A1:E214"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="36.453125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="53.1796875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="70.7265625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.81640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="97.1796875" bestFit="1" customWidth="1"/>
   </cols>
@@ -1889,7 +2327,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>67</v>
       </c>
@@ -2242,7 +2680,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>10</v>
       </c>
@@ -3095,6 +3533,809 @@
       </c>
       <c r="C141" s="1" t="s">
         <v>309</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A142" t="s">
+        <v>17</v>
+      </c>
+      <c r="B142" t="s">
+        <v>455</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A143" t="s">
+        <v>17</v>
+      </c>
+      <c r="B143" t="s">
+        <v>310</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A144" t="s">
+        <v>17</v>
+      </c>
+      <c r="B144" t="s">
+        <v>315</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A145" t="s">
+        <v>17</v>
+      </c>
+      <c r="B145" t="s">
+        <v>316</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A146" t="s">
+        <v>17</v>
+      </c>
+      <c r="B146" t="s">
+        <v>317</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A147" t="s">
+        <v>17</v>
+      </c>
+      <c r="B147" t="s">
+        <v>322</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A148" t="s">
+        <v>17</v>
+      </c>
+      <c r="B148" t="s">
+        <v>321</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A149" t="s">
+        <v>17</v>
+      </c>
+      <c r="B149" t="s">
+        <v>323</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A150" t="s">
+        <v>17</v>
+      </c>
+      <c r="B150" t="s">
+        <v>319</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A151" t="s">
+        <v>17</v>
+      </c>
+      <c r="B151" t="s">
+        <v>318</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A152" t="s">
+        <v>17</v>
+      </c>
+      <c r="B152" t="s">
+        <v>324</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A153" t="s">
+        <v>17</v>
+      </c>
+      <c r="B153" t="s">
+        <v>320</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A154" t="s">
+        <v>17</v>
+      </c>
+      <c r="B154" t="s">
+        <v>325</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A155" t="s">
+        <v>17</v>
+      </c>
+      <c r="B155" t="s">
+        <v>326</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A156" t="s">
+        <v>17</v>
+      </c>
+      <c r="B156" t="s">
+        <v>311</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A157" t="s">
+        <v>17</v>
+      </c>
+      <c r="B157" t="s">
+        <v>312</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A158" t="s">
+        <v>17</v>
+      </c>
+      <c r="B158" t="s">
+        <v>313</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A159" t="s">
+        <v>17</v>
+      </c>
+      <c r="B159" t="s">
+        <v>314</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A160" t="s">
+        <v>17</v>
+      </c>
+      <c r="B160" t="s">
+        <v>345</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A161" t="s">
+        <v>17</v>
+      </c>
+      <c r="B161" t="s">
+        <v>347</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A162" t="s">
+        <v>17</v>
+      </c>
+      <c r="B162" t="s">
+        <v>349</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A163" t="s">
+        <v>17</v>
+      </c>
+      <c r="B163" t="s">
+        <v>351</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A164" t="s">
+        <v>17</v>
+      </c>
+      <c r="B164" t="s">
+        <v>353</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A165" t="s">
+        <v>17</v>
+      </c>
+      <c r="B165" t="s">
+        <v>355</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A166" t="s">
+        <v>17</v>
+      </c>
+      <c r="B166" t="s">
+        <v>357</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A167" t="s">
+        <v>17</v>
+      </c>
+      <c r="B167" t="s">
+        <v>359</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A168" t="s">
+        <v>17</v>
+      </c>
+      <c r="B168" t="s">
+        <v>361</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A169" t="s">
+        <v>17</v>
+      </c>
+      <c r="B169" t="s">
+        <v>363</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A170" t="s">
+        <v>17</v>
+      </c>
+      <c r="B170" t="s">
+        <v>365</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A171" t="s">
+        <v>17</v>
+      </c>
+      <c r="B171" t="s">
+        <v>367</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A172" t="s">
+        <v>17</v>
+      </c>
+      <c r="B172" t="s">
+        <v>369</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A173" t="s">
+        <v>17</v>
+      </c>
+      <c r="B173" t="s">
+        <v>371</v>
+      </c>
+      <c r="C173" s="1" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A174" t="s">
+        <v>17</v>
+      </c>
+      <c r="B174" t="s">
+        <v>373</v>
+      </c>
+      <c r="C174" s="1" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A175" t="s">
+        <v>17</v>
+      </c>
+      <c r="B175" t="s">
+        <v>375</v>
+      </c>
+      <c r="C175" s="1" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A176" t="s">
+        <v>17</v>
+      </c>
+      <c r="B176" t="s">
+        <v>377</v>
+      </c>
+      <c r="C176" s="1" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A177" t="s">
+        <v>17</v>
+      </c>
+      <c r="B177" t="s">
+        <v>379</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A178" t="s">
+        <v>17</v>
+      </c>
+      <c r="B178" t="s">
+        <v>381</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A179" t="s">
+        <v>17</v>
+      </c>
+      <c r="B179" t="s">
+        <v>383</v>
+      </c>
+      <c r="C179" s="1" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A180" t="s">
+        <v>17</v>
+      </c>
+      <c r="B180" t="s">
+        <v>385</v>
+      </c>
+      <c r="C180" s="1" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A181" t="s">
+        <v>17</v>
+      </c>
+      <c r="B181" t="s">
+        <v>387</v>
+      </c>
+      <c r="C181" s="1" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A182" t="s">
+        <v>17</v>
+      </c>
+      <c r="B182" t="s">
+        <v>389</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A183" t="s">
+        <v>17</v>
+      </c>
+      <c r="B183" t="s">
+        <v>391</v>
+      </c>
+      <c r="C183" s="1" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A184" t="s">
+        <v>17</v>
+      </c>
+      <c r="B184" t="s">
+        <v>393</v>
+      </c>
+      <c r="C184" s="1" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A185" t="s">
+        <v>17</v>
+      </c>
+      <c r="B185" t="s">
+        <v>395</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A186" t="s">
+        <v>17</v>
+      </c>
+      <c r="B186" t="s">
+        <v>397</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A187" t="s">
+        <v>17</v>
+      </c>
+      <c r="B187" t="s">
+        <v>399</v>
+      </c>
+      <c r="C187" s="1" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A188" t="s">
+        <v>17</v>
+      </c>
+      <c r="B188" t="s">
+        <v>401</v>
+      </c>
+      <c r="C188" s="1" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A189" t="s">
+        <v>17</v>
+      </c>
+      <c r="B189" t="s">
+        <v>403</v>
+      </c>
+      <c r="C189" s="1" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A190" t="s">
+        <v>17</v>
+      </c>
+      <c r="B190" t="s">
+        <v>405</v>
+      </c>
+      <c r="C190" s="1" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A191" t="s">
+        <v>17</v>
+      </c>
+      <c r="B191" t="s">
+        <v>407</v>
+      </c>
+      <c r="C191" s="1" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A192" t="s">
+        <v>17</v>
+      </c>
+      <c r="B192" t="s">
+        <v>409</v>
+      </c>
+      <c r="C192" s="1" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A193" t="s">
+        <v>17</v>
+      </c>
+      <c r="B193" t="s">
+        <v>411</v>
+      </c>
+      <c r="C193" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A194" t="s">
+        <v>17</v>
+      </c>
+      <c r="B194" t="s">
+        <v>413</v>
+      </c>
+      <c r="C194" s="1" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A195" t="s">
+        <v>17</v>
+      </c>
+      <c r="B195" t="s">
+        <v>415</v>
+      </c>
+      <c r="C195" s="1" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A196" t="s">
+        <v>17</v>
+      </c>
+      <c r="B196" t="s">
+        <v>417</v>
+      </c>
+      <c r="C196" s="1" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A197" t="s">
+        <v>17</v>
+      </c>
+      <c r="B197" t="s">
+        <v>419</v>
+      </c>
+      <c r="C197" s="1" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A198" t="s">
+        <v>17</v>
+      </c>
+      <c r="B198" t="s">
+        <v>421</v>
+      </c>
+      <c r="C198" s="1" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A199" t="s">
+        <v>17</v>
+      </c>
+      <c r="B199" t="s">
+        <v>423</v>
+      </c>
+      <c r="C199" s="1" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A200" t="s">
+        <v>17</v>
+      </c>
+      <c r="B200" t="s">
+        <v>425</v>
+      </c>
+      <c r="C200" s="1" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A201" t="s">
+        <v>17</v>
+      </c>
+      <c r="B201" t="s">
+        <v>427</v>
+      </c>
+      <c r="C201" s="1" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A202" t="s">
+        <v>17</v>
+      </c>
+      <c r="B202" t="s">
+        <v>429</v>
+      </c>
+      <c r="C202" s="1" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A203" t="s">
+        <v>17</v>
+      </c>
+      <c r="B203" t="s">
+        <v>431</v>
+      </c>
+      <c r="C203" s="1" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A204" t="s">
+        <v>17</v>
+      </c>
+      <c r="B204" t="s">
+        <v>433</v>
+      </c>
+      <c r="C204" s="1" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A205" t="s">
+        <v>17</v>
+      </c>
+      <c r="B205" t="s">
+        <v>435</v>
+      </c>
+      <c r="C205" s="1" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A206" t="s">
+        <v>17</v>
+      </c>
+      <c r="B206" t="s">
+        <v>437</v>
+      </c>
+      <c r="C206" s="1" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A207" t="s">
+        <v>17</v>
+      </c>
+      <c r="B207" t="s">
+        <v>439</v>
+      </c>
+      <c r="C207" s="1" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A208" t="s">
+        <v>17</v>
+      </c>
+      <c r="B208" t="s">
+        <v>441</v>
+      </c>
+      <c r="C208" s="1" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A209" t="s">
+        <v>17</v>
+      </c>
+      <c r="B209" t="s">
+        <v>443</v>
+      </c>
+      <c r="C209" s="1" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A210" t="s">
+        <v>17</v>
+      </c>
+      <c r="B210" t="s">
+        <v>445</v>
+      </c>
+      <c r="C210" s="1" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A211" t="s">
+        <v>17</v>
+      </c>
+      <c r="B211" t="s">
+        <v>447</v>
+      </c>
+      <c r="C211" s="1" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A212" t="s">
+        <v>17</v>
+      </c>
+      <c r="B212" t="s">
+        <v>449</v>
+      </c>
+      <c r="C212" s="1" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A213" t="s">
+        <v>17</v>
+      </c>
+      <c r="B213" t="s">
+        <v>451</v>
+      </c>
+      <c r="C213" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A214" t="s">
+        <v>17</v>
+      </c>
+      <c r="B214" t="s">
+        <v>453</v>
+      </c>
+      <c r="C214" s="1" t="s">
+        <v>454</v>
       </c>
     </row>
   </sheetData>
@@ -3103,6 +4344,9 @@
       <sortCondition ref="B1:B93"/>
     </sortState>
   </autoFilter>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B142:B159">
+    <sortCondition ref="B142:B159"/>
+  </sortState>
   <hyperlinks>
     <hyperlink ref="E105" r:id="rId1" xr:uid="{D3DBCC56-4DE9-4D48-A14F-C1E905DF0FDE}"/>
   </hyperlinks>
@@ -3112,15 +4356,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002BAA57F805DE4D498A43031B16C0C8A1" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8d169cae7b697a38c1f2a3ff7bc83911">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="00850a8a-55a0-4f29-bb56-d3de9b9bc75c" xmlns:ns3="33e70369-3675-4c3b-99e1-030eb9633bdf" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3d7b88af5274db58a2019a9f8258b200" ns2:_="" ns3:_="">
     <xsd:import namespace="00850a8a-55a0-4f29-bb56-d3de9b9bc75c"/>
@@ -3367,6 +4602,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -3379,14 +4623,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7554B1E-EA5B-4036-8BEB-CEB54DFFA990}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{408CD603-C2F6-45F8-91C0-1EC5F05A3CA2}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3405,19 +4641,27 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7554B1E-EA5B-4036-8BEB-CEB54DFFA990}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13521947-7B63-4043-9A52-D2F3EDCA31C1}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="33e70369-3675-4c3b-99e1-030eb9633bdf"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="33e70369-3675-4c3b-99e1-030eb9633bdf"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="00850a8a-55a0-4f29-bb56-d3de9b9bc75c"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>